--- a/Végleges/IP cimek, alhalozat szamitas + protokollok.xlsx
+++ b/Végleges/IP cimek, alhalozat szamitas + protokollok.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peterd\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TÜRR\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4154C4ED-6FC8-4D45-B752-1AEC01ADCC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC4E419-A965-4176-9086-C96CF86897EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="361">
   <si>
     <t>Protokollok, konfigurációk, témakörök</t>
   </si>
@@ -1107,13 +1107,16 @@
   </si>
   <si>
     <t>209.165.20.255</t>
+  </si>
+  <si>
+    <t>CDP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1275,7 +1278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1319,19 +1322,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1360,23 +1350,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1389,9 +1367,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1404,18 +1379,31 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="20% - 1. jelölőszín" xfId="2" builtinId="30"/>
@@ -1703,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -1722,1224 +1710,1211 @@
     <col min="15" max="16" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:16" ht="15" customHeight="1">
+      <c r="A1" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="E1" s="26" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="E1" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="I1" s="26" t="s">
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="I1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="N1" s="29" t="s">
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="N1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75">
+      <c r="A3" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="L3" s="17"/>
-      <c r="N3" s="21" t="s">
+      <c r="L3" s="13"/>
+      <c r="N3" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:16">
+      <c r="A4" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="N4" s="18" t="s">
+      <c r="L4" s="14"/>
+      <c r="N4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="14" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:16">
+      <c r="A5" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="N5" s="18" t="s">
+      <c r="L5" s="14"/>
+      <c r="N5" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O5" s="18" t="s">
+      <c r="O5" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="14" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:16">
+      <c r="A6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="L6" s="18"/>
-      <c r="N6" s="18" t="s">
+      <c r="L6" s="14"/>
+      <c r="N6" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O6" s="18" t="s">
+      <c r="O6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="18" t="s">
+      <c r="P6" s="14" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:16">
+      <c r="A7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="18"/>
-      <c r="N7" s="18" t="s">
+      <c r="L7" s="14"/>
+      <c r="N7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="O7" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="P7" s="14" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:16">
+      <c r="A8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="L8" s="18"/>
-      <c r="N8" s="18" t="s">
+      <c r="L8" s="14"/>
+      <c r="N8" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="18" t="s">
+      <c r="O8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="P8" s="18" t="s">
+      <c r="P8" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:16">
+      <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="N9" s="18" t="s">
+      <c r="L9" s="14"/>
+      <c r="N9" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="O9" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="P9" s="14" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:16">
+      <c r="A10" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="N10" s="18" t="s">
+      <c r="L10" s="14"/>
+      <c r="N10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="18" t="s">
+      <c r="O10" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="18" t="s">
+      <c r="P10" s="14" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:16">
+      <c r="A11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="L11" s="18"/>
-      <c r="N11" s="18" t="s">
+      <c r="L11" s="14"/>
+      <c r="N11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O11" s="18" t="s">
+      <c r="O11" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="18" t="s">
+      <c r="P11" s="14" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:16">
+      <c r="A12" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="N12" s="18" t="s">
+      <c r="L12" s="14"/>
+      <c r="N12" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O12" s="18" t="s">
+      <c r="O12" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="18" t="s">
+      <c r="P12" s="14" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:16">
+      <c r="A13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="L13" s="18"/>
-      <c r="N13" s="18" t="s">
+      <c r="L13" s="14"/>
+      <c r="N13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O13" s="18" t="s">
+      <c r="O13" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="P13" s="18" t="s">
+      <c r="P13" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="I14" s="18" t="s">
+    <row r="14" spans="1:16">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="I14" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="L14" s="18"/>
-      <c r="N14" s="18" t="s">
+      <c r="L14" s="14"/>
+      <c r="N14" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O14" s="18" t="s">
+      <c r="O14" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="P14" s="18" t="s">
+      <c r="P14" s="14" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="E16" s="27" t="s">
+    <row r="15" spans="1:16">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:16" ht="15.75">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="E16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="I16" s="18" t="s">
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="I16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="L16" s="18"/>
-      <c r="N16" s="27" t="s">
+      <c r="L16" s="14"/>
+      <c r="N16" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+    </row>
+    <row r="17" spans="1:19" ht="15.75">
+      <c r="A17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="E17" s="19" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="E17" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="I17" s="20" t="s">
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="I17" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="L17" s="17"/>
-      <c r="N17" s="20" t="s">
+      <c r="L17" s="13"/>
+      <c r="N17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="O17" s="20" t="s">
+      <c r="O17" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="P17" s="18"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="P17" s="14"/>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="E18" s="19" t="s">
+      <c r="C18" s="23"/>
+      <c r="E18" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="I18" s="18" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="I18" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J18" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="L18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="E19" s="19" t="s">
+      <c r="L18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+    </row>
+    <row r="19" spans="1:19" ht="15.75">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="E19" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="N19" s="27" t="s">
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="N19" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+    </row>
+    <row r="20" spans="1:19" ht="15.75">
+      <c r="A20" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="E20" s="19" t="s">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="E20" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="I20" s="27" t="s">
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="I20" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="N20" s="19" t="s">
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="N20" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20" t="s">
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="14"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="L21" s="17" t="s">
+      <c r="L21" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="18"/>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
-      <c r="E22" s="27" t="s">
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="14"/>
+    </row>
+    <row r="22" spans="1:19" ht="15.75">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="E22" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="I22" s="17" t="s">
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="I22" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="K22" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="L22" s="17" t="s">
+      <c r="L22" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="N22" s="27" t="s">
+      <c r="N22" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="1:19" ht="15.75">
+      <c r="A23" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="E23" s="19" t="s">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="E23" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="N23" s="21" t="s">
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="N23" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="O23" s="21" t="s">
+      <c r="O23" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="P23" s="17"/>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="P23" s="13"/>
+    </row>
+    <row r="24" spans="1:19" ht="15.75">
+      <c r="A24" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="18"/>
-      <c r="N24" s="18" t="s">
+      <c r="C24" s="17"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14"/>
+      <c r="N24" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="P24" s="18"/>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="P24" s="14"/>
+    </row>
+    <row r="25" spans="1:19" ht="15.75">
+      <c r="A25" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="E25" s="27" t="s">
+      <c r="C25" s="14"/>
+      <c r="E25" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="N25" s="18" t="s">
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="N25" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="O25" s="18" t="s">
+      <c r="O25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="P25" s="18"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="P25" s="14"/>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="E26" s="19" t="s">
+      <c r="C26" s="14"/>
+      <c r="E26" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="N26" s="18" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="N26" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="O26" s="18" t="s">
+      <c r="O26" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="P26" s="18"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="P26" s="14"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="N27" s="18" t="s">
+      <c r="C27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="N27" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="O27" s="18" t="s">
+      <c r="O27" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="P27" s="18"/>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="P27" s="14"/>
+    </row>
+    <row r="28" spans="1:19" ht="15.75">
+      <c r="A28" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="E28" s="27" t="s">
+      <c r="C28" s="14"/>
+      <c r="E28" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="N28" s="18" t="s">
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="N28" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="O28" s="18" t="s">
+      <c r="O28" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="P28" s="18"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="P28" s="14"/>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18" t="s">
+      <c r="C29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="N29" s="18" t="s">
+      <c r="N29" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="O29" s="18" t="s">
+      <c r="O29" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="P29" s="18"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="P29" s="14"/>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="E30" s="18" t="s">
+      <c r="C30" s="14"/>
+      <c r="E30" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="N30" s="18" t="s">
+      <c r="N30" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="O30" s="18" t="s">
+      <c r="O30" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="P30" s="18"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="P30" s="14"/>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18" t="s">
+      <c r="C31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="N31" s="18" t="s">
+      <c r="N31" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="O31" s="18" t="s">
+      <c r="O31" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="P31" s="18"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="P31" s="14"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="E32" s="18" t="s">
+      <c r="C32" s="14"/>
+      <c r="E32" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18" t="s">
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+    </row>
+    <row r="33" spans="1:16" ht="15.75">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="N33" s="27" t="s">
+      <c r="N33" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="N34" s="22" t="s">
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+    </row>
+    <row r="34" spans="1:16" ht="15.75">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="N34" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="O34" s="22" t="s">
+      <c r="O34" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="P34" s="22" t="s">
+      <c r="P34" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="35" spans="1:16" ht="15.75">
+      <c r="A35" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="E35" s="27" t="s">
+      <c r="C35" s="17"/>
+      <c r="E35" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="N35" s="18" t="s">
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="N35" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="O35" s="18" t="s">
+      <c r="O35" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="P35" s="18" t="s">
+      <c r="P35" s="14" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
+    <row r="36" spans="1:16">
+      <c r="A36" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="E36" s="18" t="s">
+      <c r="C36" s="14"/>
+      <c r="E36" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+    </row>
+    <row r="37" spans="1:16" ht="15.75">
+      <c r="A37" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="E37" s="18" t="s">
+      <c r="C37" s="14"/>
+      <c r="E37" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="N37" s="25" t="s">
+      <c r="N37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="O37" s="25" t="s">
+      <c r="O37" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="P37" s="18"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="P37" s="14"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="E38" s="18" t="s">
+      <c r="C38" s="14"/>
+      <c r="E38" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="N38" s="18" t="s">
+      <c r="N38" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="O38" s="18" t="s">
+      <c r="O38" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="P38" s="18"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="P38" s="14"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="E39" s="18" t="s">
+      <c r="C39" s="14"/>
+      <c r="E39" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="N39" s="18" t="s">
+      <c r="N39" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="O39" s="18" t="s">
+      <c r="O39" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="P39" s="18"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="N40" s="20" t="s">
+      <c r="P39" s="14"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="N40" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="O40" s="20" t="s">
+      <c r="O40" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="P40" s="18"/>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="27" t="s">
+      <c r="P40" s="14"/>
+    </row>
+    <row r="41" spans="1:16" ht="15.75">
+      <c r="A41" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="E41" s="25" t="s">
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="E41" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="25" t="s">
+      <c r="F41" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="25"/>
-      <c r="N41" s="20" t="s">
+      <c r="G41" s="20"/>
+      <c r="N41" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="O41" s="20" t="s">
+      <c r="O41" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="P41" s="18"/>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="27" t="s">
+      <c r="P41" s="14"/>
+    </row>
+    <row r="42" spans="1:16" ht="15.75">
+      <c r="A42" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="E42" s="28" t="s">
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="E42" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="G42" s="20"/>
-      <c r="N42" s="24" t="s">
+      <c r="G42" s="15"/>
+      <c r="N42" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="O42" s="24" t="s">
+      <c r="O42" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="P42" s="18"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E43" s="23" t="s">
+      <c r="P42" s="14"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="E43" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="G43" s="17"/>
-      <c r="N43" s="24" t="s">
+      <c r="G43" s="13"/>
+      <c r="N43" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="O43" s="24" t="s">
+      <c r="O43" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="P43" s="17"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E44" s="18" t="s">
+      <c r="P43" s="13"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="E44" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="G44" s="18"/>
-      <c r="N44" s="18" t="s">
+      <c r="G44" s="14"/>
+      <c r="N44" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="O44" s="24" t="s">
+      <c r="O44" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="P44" s="18"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E45" s="18" t="s">
+      <c r="P44" s="14"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="E45" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E46" s="18" t="s">
+      <c r="G45" s="14"/>
+      <c r="N45" s="14"/>
+      <c r="O45" s="14"/>
+      <c r="P45" s="14"/>
+    </row>
+    <row r="46" spans="1:16" ht="15.75">
+      <c r="E46" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="G46" s="18"/>
-      <c r="N46" s="27" t="s">
+      <c r="G46" s="14"/>
+      <c r="N46" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E47" s="18" t="s">
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+    </row>
+    <row r="47" spans="1:16" ht="15.75">
+      <c r="E47" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="G47" s="18"/>
-      <c r="N47" s="27" t="s">
+      <c r="G47" s="14"/>
+      <c r="N47" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-    </row>
-    <row r="49" spans="5:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E49" s="27" t="s">
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+    </row>
+    <row r="49" spans="5:7" ht="15.75">
+      <c r="E49" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-    </row>
-    <row r="50" spans="5:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E50" s="27" t="s">
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+    </row>
+    <row r="50" spans="5:7" ht="15.75">
+      <c r="E50" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="N16:P16"/>
     <mergeCell ref="I1:K2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="E21:F21"/>
@@ -2947,14 +2922,27 @@
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:G2"/>
     <mergeCell ref="N1:P2"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2964,607 +2952,607 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4753624C-6DAB-430E-8AAF-D2441ACA6E99}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="9" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:5">
+      <c r="A13" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:5">
+      <c r="A19" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="10" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="10" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3575,8 +3563,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18627AFB-5308-4827-BA62-C309B61FE4A1}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -3585,17 +3573,17 @@
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7"/>
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="6"/>
+      <c r="B1" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -3611,7 +3599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3626,7 +3614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3637,7 +3625,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3650,7 +3638,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -3661,7 +3649,7 @@
       <c r="D6" s="3"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3676,7 +3664,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3691,7 +3679,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3702,7 +3690,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -3717,7 +3705,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -3728,7 +3716,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,7 +3729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3758,7 +3746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -3769,7 +3757,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -3784,7 +3772,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -3795,7 +3783,7 @@
       </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -3810,7 +3798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -3823,7 +3811,7 @@
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -3838,7 +3826,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3855,7 +3843,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -3868,7 +3856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -3879,7 +3867,7 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -3890,8 +3878,8 @@
       <c r="D23" s="3"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="4"/>
@@ -3900,6 +3888,21 @@
         <v>26</v>
       </c>
       <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
